--- a/SharePoint-Migration-ProjectPlan.xlsx
+++ b/SharePoint-Migration-ProjectPlan.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>March 18, 2026 15:02</t>
+          <t>March 18, 2026 15:10</t>
         </is>
       </c>
     </row>
